--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_12.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_12.xlsx
@@ -480,25 +480,25 @@
         <v>45992</v>
       </c>
       <c r="B5" t="n">
-        <v>1480.1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1075.86</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>291.26</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1621</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>405743</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>67085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45993</v>
       </c>
       <c r="B6" t="n">
-        <v>971.29</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>16.44</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>705.24</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>194.62</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1902</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>274361</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>40748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45994</v>
       </c>
       <c r="B7" t="n">
-        <v>916.89</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>667.4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>185.83</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1554</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>243732</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>39972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45995</v>
       </c>
       <c r="B8" t="n">
-        <v>951.29</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>14.99</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>684.54</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>185.85</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1774</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>246248</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>43072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45996</v>
       </c>
       <c r="B9" t="n">
-        <v>870.29</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>14.04</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>629.92</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>170.14</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>224915</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>40365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45997</v>
       </c>
       <c r="B10" t="n">
-        <v>1135.65</v>
+        <v>804.75</v>
       </c>
       <c r="C10" t="n">
-        <v>17.49</v>
+        <v>12.22</v>
       </c>
       <c r="D10" t="n">
-        <v>818.49</v>
+        <v>585.41</v>
       </c>
       <c r="E10" t="n">
-        <v>229.13</v>
+        <v>155.07</v>
       </c>
       <c r="F10" t="n">
-        <v>2112</v>
+        <v>780</v>
       </c>
       <c r="G10" t="n">
-        <v>346437</v>
+        <v>237486</v>
       </c>
       <c r="H10" t="n">
-        <v>50172</v>
+        <v>36311</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45998</v>
       </c>
       <c r="B11" t="n">
-        <v>688.39</v>
+        <v>1403.08</v>
       </c>
       <c r="C11" t="n">
-        <v>11.42</v>
+        <v>23.35</v>
       </c>
       <c r="D11" t="n">
-        <v>496.77</v>
+        <v>1007.53</v>
       </c>
       <c r="E11" t="n">
-        <v>135.26</v>
+        <v>278.53</v>
       </c>
       <c r="F11" t="n">
-        <v>1298</v>
+        <v>1112</v>
       </c>
       <c r="G11" t="n">
-        <v>216495</v>
+        <v>397321</v>
       </c>
       <c r="H11" t="n">
-        <v>28955</v>
+        <v>65224</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45999</v>
       </c>
       <c r="B12" t="n">
-        <v>508.85</v>
+        <v>1337.52</v>
       </c>
       <c r="C12" t="n">
-        <v>8.220000000000001</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>368.22</v>
+        <v>974.33</v>
       </c>
       <c r="E12" t="n">
-        <v>104.78</v>
+        <v>265.55</v>
       </c>
       <c r="F12" t="n">
-        <v>1155</v>
+        <v>1190</v>
       </c>
       <c r="G12" t="n">
-        <v>132832</v>
+        <v>374558</v>
       </c>
       <c r="H12" t="n">
-        <v>22639</v>
+        <v>60685</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>46000</v>
       </c>
       <c r="B13" t="n">
-        <v>445.12</v>
+        <v>1499.27</v>
       </c>
       <c r="C13" t="n">
-        <v>6.85</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>323.47</v>
+        <v>1080.78</v>
       </c>
       <c r="E13" t="n">
-        <v>88.12</v>
+        <v>298.64</v>
       </c>
       <c r="F13" t="n">
-        <v>906</v>
+        <v>1414</v>
       </c>
       <c r="G13" t="n">
-        <v>130755</v>
+        <v>414103</v>
       </c>
       <c r="H13" t="n">
-        <v>19864</v>
+        <v>68246</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>46001</v>
       </c>
       <c r="B14" t="n">
-        <v>264.13</v>
+        <v>867.78</v>
       </c>
       <c r="C14" t="n">
-        <v>4.29</v>
+        <v>14.11</v>
       </c>
       <c r="D14" t="n">
-        <v>190.56</v>
+        <v>637.23</v>
       </c>
       <c r="E14" t="n">
-        <v>53.67</v>
+        <v>171.32</v>
       </c>
       <c r="F14" t="n">
-        <v>453</v>
+        <v>1079</v>
       </c>
       <c r="G14" t="n">
-        <v>80221</v>
+        <v>224166</v>
       </c>
       <c r="H14" t="n">
-        <v>12692</v>
+        <v>39743</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>46002</v>
       </c>
       <c r="B15" t="n">
-        <v>391.41</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>283.38</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>78.87</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>593</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>116173</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>18103</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>46003</v>
       </c>
       <c r="B16" t="n">
-        <v>484.6</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>7.28</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>350.83</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>97.08</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1021</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>135529</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>21189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9108.01</v>
+        <v>5912.4</v>
       </c>
       <c r="C37" t="n">
-        <v>146.06</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>6594.679999999999</v>
+        <v>4285.28</v>
       </c>
       <c r="E37" t="n">
-        <v>1814.61</v>
+        <v>1169.11</v>
       </c>
       <c r="F37" t="n">
-        <v>16053</v>
+        <v>5575</v>
       </c>
       <c r="G37" t="n">
-        <v>2553441</v>
+        <v>1647634</v>
       </c>
       <c r="H37" t="n">
-        <v>404856</v>
+        <v>270209</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_12.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_12.xlsx
@@ -480,25 +480,25 @@
         <v>45992</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1472.03</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1070.86</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>298.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>388724</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>64858</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45993</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1487.6</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1080.96</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>310.44</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1382</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>421279</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>70359</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45994</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>888.0700000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>13.69</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>640.6799999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>177.42</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>214319</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>37043</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45995</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1471.35</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1073.69</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>294.32</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>394613</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>64280</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45996</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1446.91</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1061.78</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>290.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1277</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>366300</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>66427</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45997</v>
       </c>
       <c r="B10" t="n">
-        <v>804.75</v>
+        <v>1321.89</v>
       </c>
       <c r="C10" t="n">
-        <v>12.22</v>
+        <v>22.38</v>
       </c>
       <c r="D10" t="n">
-        <v>585.41</v>
+        <v>957.3099999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>155.07</v>
+        <v>261.15</v>
       </c>
       <c r="F10" t="n">
-        <v>780</v>
+        <v>1300</v>
       </c>
       <c r="G10" t="n">
-        <v>237486</v>
+        <v>334729</v>
       </c>
       <c r="H10" t="n">
-        <v>36311</v>
+        <v>61194</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45998</v>
       </c>
       <c r="B11" t="n">
-        <v>1403.08</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.35</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1007.53</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>278.53</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1112</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>397321</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>65224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45999</v>
       </c>
       <c r="B12" t="n">
-        <v>1337.52</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>974.33</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>265.55</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1190</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>374558</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>60685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>46000</v>
       </c>
       <c r="B13" t="n">
-        <v>1499.27</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1080.78</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>298.64</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1414</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>414103</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>68246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>46001</v>
       </c>
       <c r="B14" t="n">
-        <v>867.78</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.11</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>637.23</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>171.32</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1079</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>224166</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>39743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -766,25 +766,25 @@
         <v>46003</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1297.6</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>21.33</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>943.14</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>257.33</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1244</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>353068</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>60244</v>
       </c>
     </row>
     <row r="17">
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5912.4</v>
+        <v>9385.450000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>97.68000000000001</v>
+        <v>152.8</v>
       </c>
       <c r="D37" t="n">
-        <v>4285.28</v>
+        <v>6828.42</v>
       </c>
       <c r="E37" t="n">
-        <v>1169.11</v>
+        <v>1889.46</v>
       </c>
       <c r="F37" t="n">
-        <v>5575</v>
+        <v>8887</v>
       </c>
       <c r="G37" t="n">
-        <v>1647634</v>
+        <v>2473032</v>
       </c>
       <c r="H37" t="n">
-        <v>270209</v>
+        <v>424405</v>
       </c>
     </row>
   </sheetData>
